--- a/data/trans_orig/IP16A07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A07-Estudios-trans_orig.xlsx
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>36257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143939</t>
+          <t>143453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301250</t>
+          <t>302149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117124</t>
+          <t>116493</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237271</t>
+          <t>237639</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37128</t>
+          <t>36482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83115</t>
+          <t>83323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171033</t>
+          <t>171965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177170</t>
+          <t>177218</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>354179</t>
+          <t>354228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>359340</t>
+          <t>359361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A07-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,107 +2326,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3641</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,9%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>16,14%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3647</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3824</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21925</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18940</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18935</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,1%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>83,86%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>56</t>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36257</t>
+          <t>36434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>88236</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3125,47 +3125,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>36404</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3768</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3462</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>146565</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>143453</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>143966</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>433</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302149</t>
+          <t>301725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147221</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4042,47 +4042,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15691</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4385,47 +4385,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>82979</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4728,47 +4728,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>28792</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5071,47 +5071,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5645,64 +5645,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9781</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15667</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,107 +5875,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4350</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3054</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3228</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5988,74 +5988,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>120130</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>116493</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>92031</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>89877</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>92684</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>120024</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>317</t>
@@ -6063,27 +6063,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>240154</t>
+          <t>199943</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237639</t>
+          <t>197542</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,107 +6218,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5160</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4795</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,39%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>11,83%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5341</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4830</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -6331,74 +6331,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>40237</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36482</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>39120</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>35732</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>40527</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>88,17%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>46511</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>120</t>
@@ -6406,27 +6406,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>86748</t>
+          <t>82240</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83323</t>
+          <t>78306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5750</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>175597</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>171965</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>177218</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>140931</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>142464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>357798</t>
+          <t>305883</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>354228</t>
+          <t>301474</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>359361</t>
+          <t>307395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
